--- a/Results/TablesForBook.xlsx
+++ b/Results/TablesForBook.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jason.debacker/repos/RedesigningAging/Results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5859FA99-4FE4-9946-B5B8-0AFF09F646F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{317CDD2D-1DEC-2341-8AD5-86E5D76CF467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1120" windowWidth="30240" windowHeight="17080" xr2:uid="{4BA2160B-CE8A-FD43-9C3B-072358C868E3}"/>
+    <workbookView xWindow="46660" yWindow="500" windowWidth="29800" windowHeight="28240" activeTab="5" xr2:uid="{4BA2160B-CE8A-FD43-9C3B-072358C868E3}"/>
   </bookViews>
   <sheets>
     <sheet name="raw_output" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="176">
   <si>
     <t>age_effect</t>
   </si>
@@ -230,22 +230,6 @@
   </si>
   <si>
     <t>Future 1: Slowing Brain Aging</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Annual change
-in U.S. GDP
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Garamond"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">(Avg. 2045-2064) </t>
-    </r>
   </si>
   <si>
     <t>Future 2: Slowing Reproductive Aging</t>
@@ -693,25 +677,6 @@
     <t>Notes: Total product and QALY results come from the OG-USA model, assuming 100% adherence to the treatment.  The $160,000 QALY represents an inflation-adjusted value for the QALY estimate used in Cutler (2004), putting the value in 2025 dollars.  Theoretical VSL values are from Scott et al. (2021), adjusted for inflation to put in 2025 dollars.  *Scott et al. (2021) methods do not allow for a decomposition of annual effects.</t>
   </si>
   <si>
-    <t>Additional Adults Alive in 2050</t>
-  </si>
-  <si>
-    <r>
-      <t>Average change
-in U.S. GDP
-over first 20 years</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Garamond"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t>Increase in GDP per capita over first 20 years</t>
   </si>
   <si>
@@ -746,6 +711,25 @@
   </si>
   <si>
     <t>Additional Living People in 2050</t>
+  </si>
+  <si>
+    <t>Lives saved or gained</t>
+  </si>
+  <si>
+    <r>
+      <t>Average change
+in US GDP
+over first 20 years</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Garamond"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1151,7 +1135,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -1324,6 +1308,17 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1370,7 +1365,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1498,16 +1493,21 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -3149,10 +3149,10 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="J1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="K1" t="s">
         <v>9</v>
@@ -3167,10 +3167,10 @@
         <v>12</v>
       </c>
       <c r="O1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="P1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -12993,7 +12993,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -13012,13 +13012,13 @@
         <v>21</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="E2" s="11" t="s">
         <v>23</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="17" thickTop="1" x14ac:dyDescent="0.2">
@@ -13063,7 +13063,7 @@
         <v>$10.6T</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -13085,7 +13085,7 @@
         <v>$8.0T</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -13113,7 +13113,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="51" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B7" s="51"/>
       <c r="C7" s="51"/>
@@ -13147,7 +13147,7 @@
     </row>
     <row r="13" spans="1:6" ht="21" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -13157,22 +13157,22 @@
     </row>
     <row r="14" spans="1:6" ht="67" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="B14" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="C14" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>123</v>
-      </c>
       <c r="D14" s="10" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="E14" s="11" t="s">
         <v>23</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="17" thickTop="1" x14ac:dyDescent="0.2">
@@ -13217,7 +13217,7 @@
         <v>$9.9T</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
@@ -13239,7 +13239,7 @@
         <v>$8.7T</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
@@ -13254,20 +13254,20 @@
       </c>
       <c r="D18" s="16" t="str">
         <f>'Overall Output. Labeled'!J30</f>
-        <v>$B</v>
+        <v>$274B</v>
       </c>
       <c r="E18" s="16" t="str">
         <f>'Overall Output. Labeled'!K30</f>
-        <v>$.0T</v>
+        <v>$21.0T</v>
       </c>
       <c r="F18" s="16" t="str">
         <f>'Overall Output. Labeled'!L30</f>
-        <v>k</v>
+        <v>743k</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19" s="51" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B19" s="51"/>
       <c r="C19" s="51"/>
@@ -13309,48 +13309,48 @@
     </row>
     <row r="25" spans="1:14" ht="21" x14ac:dyDescent="0.25">
       <c r="A25" s="14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="81" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="56" t="s">
+      <c r="B26" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="C26" s="56"/>
+      <c r="C26" s="55"/>
       <c r="I26" s="10" t="s">
         <v>41</v>
       </c>
       <c r="J26" s="45" t="s">
+        <v>152</v>
+      </c>
+      <c r="K26" s="45" t="s">
         <v>153</v>
       </c>
-      <c r="K26" s="45" t="s">
+      <c r="L26" s="45" t="s">
         <v>154</v>
       </c>
-      <c r="L26" s="45" t="s">
+      <c r="M26" s="45" t="s">
         <v>155</v>
       </c>
-      <c r="M26" s="45" t="s">
+      <c r="N26" s="45" t="s">
         <v>156</v>
-      </c>
-      <c r="N26" s="45" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A27" s="25">
         <v>0.01</v>
       </c>
-      <c r="B27" s="57" t="str">
+      <c r="B27" s="56" t="str">
         <f>'Overall Output. Labeled'!K31</f>
-        <v>$.0T</v>
-      </c>
-      <c r="C27" s="57"/>
+        <v>$53.3T</v>
+      </c>
+      <c r="C27" s="56"/>
       <c r="I27" s="25">
         <v>0.01</v>
       </c>
@@ -13379,11 +13379,11 @@
       <c r="A28" s="25">
         <v>0.02</v>
       </c>
-      <c r="B28" s="55" t="str">
+      <c r="B28" s="57" t="str">
         <f>'Overall Output. Labeled'!K13</f>
         <v>$27.1T</v>
       </c>
-      <c r="C28" s="55"/>
+      <c r="C28" s="57"/>
       <c r="I28" s="25">
         <v>0.02</v>
       </c>
@@ -13412,11 +13412,11 @@
       <c r="A29" s="25">
         <v>0.03</v>
       </c>
-      <c r="B29" s="55" t="str">
+      <c r="B29" s="57" t="str">
         <f>'Overall Output. Labeled'!K32</f>
         <v>$14.6T</v>
       </c>
-      <c r="C29" s="55"/>
+      <c r="C29" s="57"/>
       <c r="I29" s="25">
         <v>0.03</v>
       </c>
@@ -13445,11 +13445,11 @@
       <c r="A30" s="25">
         <v>0.04</v>
       </c>
-      <c r="B30" s="55" t="str">
+      <c r="B30" s="57" t="str">
         <f>'Overall Output. Labeled'!K33</f>
         <v>$8.3T</v>
       </c>
-      <c r="C30" s="55"/>
+      <c r="C30" s="57"/>
       <c r="I30" s="46">
         <v>0.04</v>
       </c>
@@ -13478,13 +13478,13 @@
       <c r="A31" s="25">
         <v>0.05</v>
       </c>
-      <c r="B31" s="55" t="str">
+      <c r="B31" s="57" t="str">
         <f>'Overall Output. Labeled'!K34</f>
         <v>$5.0T</v>
       </c>
-      <c r="C31" s="55"/>
+      <c r="C31" s="57"/>
       <c r="I31" s="51" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J31" s="51"/>
       <c r="K31" s="51"/>
@@ -13494,7 +13494,7 @@
     </row>
     <row r="32" spans="1:14" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="51" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B32" s="51"/>
       <c r="C32" s="51"/>
@@ -13604,19 +13604,19 @@
         <v>41</v>
       </c>
       <c r="J42" s="45" t="s">
+        <v>152</v>
+      </c>
+      <c r="K42" s="45" t="s">
         <v>153</v>
       </c>
-      <c r="K42" s="45" t="s">
+      <c r="L42" s="45" t="s">
         <v>154</v>
       </c>
-      <c r="L42" s="45" t="s">
+      <c r="M42" s="45" t="s">
         <v>155</v>
       </c>
-      <c r="M42" s="45" t="s">
+      <c r="N42" s="45" t="s">
         <v>156</v>
-      </c>
-      <c r="N42" s="45" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="17" thickTop="1" x14ac:dyDescent="0.2">
@@ -13701,16 +13701,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="I31:N39"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="A32:C36"/>
     <mergeCell ref="A7:F10"/>
     <mergeCell ref="A19:F22"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B28:C28"/>
-    <mergeCell ref="I31:N39"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="A32:C36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -13801,7 +13801,7 @@
         <v>23</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="M2" s="5" t="s">
         <v>49</v>
@@ -14022,7 +14022,7 @@
         <f>IF(V5&gt;1000,_xlfn.CONCAT(TEXT(V5/1000,"$#.0"),"T"),_xlfn.CONCAT(TEXT(V5,"$#"),"B"))</f>
         <v>$118B</v>
       </c>
-      <c r="K5" s="58" t="str">
+      <c r="K5" s="8" t="str">
         <f>_xlfn.CONCAT(TEXT(SUMIFS(raw_output!$N$2:$N$197,raw_output!$M$2:$M$197,'Overall Output. Labeled'!$N5,raw_output!$A$2:$A$197,'Overall Output. Labeled'!$U5,raw_output!$B$2:$B$197,'Overall Output. Labeled'!$S5,raw_output!$C$2:$C$197,'Overall Output. Labeled'!$T5,raw_output!$D$2:$D$197,'Overall Output. Labeled'!$P5,raw_output!$E$2:$E$197,'Overall Output. Labeled'!$Q5,raw_output!$F$2:$F$197,'Overall Output. Labeled'!$R5),"$#.0"),"T")</f>
         <v>$6.8T</v>
       </c>
@@ -14232,7 +14232,7 @@
       <c r="A8" s="8"/>
       <c r="B8" s="8"/>
       <c r="C8" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
@@ -14381,7 +14381,7 @@
       <c r="A10" s="32"/>
       <c r="B10" s="32"/>
       <c r="C10" s="32" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="32"/>
@@ -14394,7 +14394,7 @@
         <v>$426B</v>
       </c>
       <c r="K10" s="34" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="L10" s="32" t="str">
         <f t="shared" si="2"/>
@@ -14501,7 +14501,7 @@
       <c r="A12" s="32"/>
       <c r="B12" s="32"/>
       <c r="C12" s="32" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D12" s="32"/>
       <c r="E12" s="32"/>
@@ -14510,10 +14510,10 @@
       <c r="H12" s="32"/>
       <c r="I12" s="32"/>
       <c r="J12" s="32" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K12" s="34" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="L12" s="32" t="str">
         <f t="shared" si="2"/>
@@ -14867,7 +14867,7 @@
         <v>40</v>
       </c>
       <c r="C17" s="35" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D17" s="35"/>
       <c r="E17" s="35" t="s">
@@ -14922,7 +14922,7 @@
         <v>40</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D18" s="8" t="s">
         <v>39</v>
@@ -15020,7 +15020,7 @@
       </c>
       <c r="J19" s="35"/>
       <c r="K19" s="49" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="L19" s="35"/>
       <c r="M19" s="35"/>
@@ -15075,19 +15075,19 @@
       </c>
       <c r="J20" s="8" t="str">
         <f>IF(V20&gt;1000,_xlfn.CONCAT(TEXT(V20/1000,"$#.0"),"T"),_xlfn.CONCAT(TEXT(V20,"$#"),"B"))</f>
-        <v>$B</v>
+        <v>$715B</v>
       </c>
       <c r="K20" s="8" t="str">
         <f>_xlfn.CONCAT(TEXT(SUMIFS(raw_output!$N$2:$N$197,raw_output!$M$2:$M$197,'Overall Output. Labeled'!$N20,raw_output!$A$2:$A$197,'Overall Output. Labeled'!$U20,raw_output!$B$2:$B$197,'Overall Output. Labeled'!$S20,raw_output!$C$2:$C$197,'Overall Output. Labeled'!$T20,raw_output!$D$2:$D$197,'Overall Output. Labeled'!$P20,raw_output!$E$2:$E$197,'Overall Output. Labeled'!$Q20,raw_output!$F$2:$F$197,'Overall Output. Labeled'!$R20),"$#.0"),"T")</f>
-        <v>$.0T</v>
+        <v>$38.4T</v>
       </c>
       <c r="L20" s="8" t="str">
         <f>IF(W20&gt;1000,_xlfn.CONCAT(TEXT(W20/1000,"#.#"),"M"),_xlfn.CONCAT(TEXT(W20,"#"),"k"))</f>
-        <v>k</v>
+        <v>6.5M</v>
       </c>
       <c r="M20" s="8" t="str">
         <f>TEXT(SUMIFS(raw_output!$L$2:$L$197,raw_output!$M$2:$M$197,'Overall Output. Labeled'!$N20,raw_output!$A$2:$A$197,'Overall Output. Labeled'!$U20,raw_output!$B$2:$B$197,'Overall Output. Labeled'!$S20,raw_output!$C$2:$C$197,'Overall Output. Labeled'!$T20,raw_output!$D$2:$D$197,'Overall Output. Labeled'!$P20,raw_output!$E$2:$E$197,'Overall Output. Labeled'!$Q20,raw_output!$F$2:$F$197,'Overall Output. Labeled'!$R20),"$#.##")</f>
-        <v>$.</v>
+        <v>-$2229.5</v>
       </c>
       <c r="N20" s="8">
         <v>0.02</v>
@@ -15100,8 +15100,7 @@
         <v>2.52</v>
       </c>
       <c r="Q20" s="8">
-        <f>G20*$O20</f>
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="R20" s="34">
         <v>0</v>
@@ -15117,11 +15116,11 @@
       </c>
       <c r="V20" s="8">
         <f>SUMIFS(raw_output!$K$2:$K$197,raw_output!$A$2:$A$197,'Overall Output. Labeled'!$U20,raw_output!$B$2:$B$197,'Overall Output. Labeled'!$S20,raw_output!$C$2:$C$197,'Overall Output. Labeled'!$T20,raw_output!$D$2:$D$197,'Overall Output. Labeled'!$P20,raw_output!$E$2:$E$197,'Overall Output. Labeled'!$Q20,raw_output!$F$2:$F$197,'Overall Output. Labeled'!$R20,raw_output!$M$2:$M$197,'Overall Output. Labeled'!$N20)</f>
-        <v>0</v>
+        <v>714.84513741596902</v>
       </c>
       <c r="W20" s="8">
         <f t="array" ref="W20">SUMIFS(raw_output!$J$2:$J$197,raw_output!$M$2:$M$197,'Overall Output. Labeled'!$N20,raw_output!$A$2:$A$197,'Overall Output. Labeled'!$U20,raw_output!$B$2:$B$197,'Overall Output. Labeled'!$S20,raw_output!$C$2:$C$197,'Overall Output. Labeled'!$T20,raw_output!$D$2:$D$197,'Overall Output. Labeled'!$P20,raw_output!$E$2:$E$197,'Overall Output. Labeled'!$Q20,raw_output!$F$2:$F$197,'Overall Output. Labeled'!$R20)*1000</f>
-        <v>0</v>
+        <v>6529.4666553730203</v>
       </c>
     </row>
     <row r="21" spans="1:23" x14ac:dyDescent="0.2">
@@ -15224,7 +15223,7 @@
       </c>
       <c r="J22" s="35"/>
       <c r="K22" s="49" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="L22" s="35"/>
       <c r="M22" s="35"/>
@@ -15555,7 +15554,7 @@
       </c>
       <c r="B27" s="8"/>
       <c r="C27" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
@@ -15585,8 +15584,8 @@
       <c r="N27" s="8">
         <v>0.02</v>
       </c>
-      <c r="O27" s="8" t="s">
-        <v>40</v>
+      <c r="O27" s="8">
+        <v>1</v>
       </c>
       <c r="P27" s="8">
         <v>0.13</v>
@@ -15653,8 +15652,8 @@
       <c r="N28" s="8">
         <v>0.02</v>
       </c>
-      <c r="O28" s="8" t="s">
-        <v>40</v>
+      <c r="O28" s="8">
+        <v>1</v>
       </c>
       <c r="P28" s="8">
         <f t="shared" ref="P28:P29" si="12">F28</f>
@@ -15721,8 +15720,8 @@
       <c r="N29" s="8">
         <v>0.02</v>
       </c>
-      <c r="O29" s="8" t="s">
-        <v>40</v>
+      <c r="O29" s="8">
+        <v>1</v>
       </c>
       <c r="P29" s="8">
         <f t="shared" si="12"/>
@@ -15772,25 +15771,25 @@
       </c>
       <c r="J30" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>$B</v>
+        <v>$274B</v>
       </c>
       <c r="K30" s="8" t="str">
         <f>_xlfn.CONCAT(TEXT(SUMIFS(raw_output!$N$2:$N$197,raw_output!$M$2:$M$197,'Overall Output. Labeled'!$N30,raw_output!$A$2:$A$197,'Overall Output. Labeled'!$U30,raw_output!$B$2:$B$197,'Overall Output. Labeled'!$S30,raw_output!$C$2:$C$197,'Overall Output. Labeled'!$T30,raw_output!$D$2:$D$197,'Overall Output. Labeled'!$P30,raw_output!$E$2:$E$197,'Overall Output. Labeled'!$Q30,raw_output!$F$2:$F$197,'Overall Output. Labeled'!$R30),"$#.0"),"T")</f>
-        <v>$.0T</v>
+        <v>$21.0T</v>
       </c>
       <c r="L30" s="8" t="str">
         <f t="shared" si="8"/>
-        <v>k</v>
+        <v>743k</v>
       </c>
       <c r="M30" s="8" t="str">
         <f>TEXT(SUMIFS(raw_output!$L$2:$L$197,raw_output!$M$2:$M$197,'Overall Output. Labeled'!$N30,raw_output!$A$2:$A$197,'Overall Output. Labeled'!$U30,raw_output!$B$2:$B$197,'Overall Output. Labeled'!$S30,raw_output!$C$2:$C$197,'Overall Output. Labeled'!$T30,raw_output!$D$2:$D$197,'Overall Output. Labeled'!$P30,raw_output!$E$2:$E$197,'Overall Output. Labeled'!$Q30,raw_output!$F$2:$F$197,'Overall Output. Labeled'!$R30),"$#.##")</f>
-        <v>$.</v>
+        <v>$681.02</v>
       </c>
       <c r="N30" s="8">
         <v>0.02</v>
       </c>
-      <c r="O30" s="8" t="s">
-        <v>40</v>
+      <c r="O30" s="8">
+        <v>1</v>
       </c>
       <c r="P30" s="8">
         <v>0.13</v>
@@ -15805,18 +15804,18 @@
         <v>10</v>
       </c>
       <c r="T30" s="8">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="U30" s="8">
         <v>40</v>
       </c>
       <c r="V30" s="8">
         <f>SUMIFS(raw_output!$K$2:$K$197,raw_output!$A$2:$A$197,'Overall Output. Labeled'!$U30,raw_output!$B$2:$B$197,'Overall Output. Labeled'!$S30,raw_output!$C$2:$C$197,'Overall Output. Labeled'!$T30,raw_output!$D$2:$D$197,'Overall Output. Labeled'!$P30,raw_output!$E$2:$E$197,'Overall Output. Labeled'!$Q30,raw_output!$F$2:$F$197,'Overall Output. Labeled'!$R30,raw_output!$M$2:$M$197,'Overall Output. Labeled'!$N30)</f>
-        <v>0</v>
+        <v>274.08749956012298</v>
       </c>
       <c r="W30" s="8">
         <f t="array" ref="W30">SUMIFS(raw_output!$J$2:$J$197,raw_output!$M$2:$M$197,'Overall Output. Labeled'!$N30,raw_output!$A$2:$A$197,'Overall Output. Labeled'!$U30,raw_output!$B$2:$B$197,'Overall Output. Labeled'!$S30,raw_output!$C$2:$C$197,'Overall Output. Labeled'!$T30,raw_output!$D$2:$D$197,'Overall Output. Labeled'!$P30,raw_output!$E$2:$E$197,'Overall Output. Labeled'!$Q30,raw_output!$F$2:$F$197,'Overall Output. Labeled'!$R30)*1000</f>
-        <v>0</v>
+        <v>742.72154631445994</v>
       </c>
     </row>
     <row r="31" spans="1:23" x14ac:dyDescent="0.2">
@@ -15844,19 +15843,19 @@
       </c>
       <c r="J31" s="8" t="str">
         <f t="shared" si="7"/>
-        <v>$B</v>
+        <v>$408B</v>
       </c>
       <c r="K31" s="8" t="str">
         <f>_xlfn.CONCAT(TEXT(SUMIFS(raw_output!$N$2:$N$197,raw_output!$M$2:$M$197,'Overall Output. Labeled'!$N31,raw_output!$A$2:$A$197,'Overall Output. Labeled'!$U31,raw_output!$B$2:$B$197,'Overall Output. Labeled'!$S31,raw_output!$C$2:$C$197,'Overall Output. Labeled'!$T31,raw_output!$D$2:$D$197,'Overall Output. Labeled'!$P31,raw_output!$E$2:$E$197,'Overall Output. Labeled'!$Q31,raw_output!$F$2:$F$197,'Overall Output. Labeled'!$R31),"$#.0"),"T")</f>
-        <v>$.0T</v>
+        <v>$53.3T</v>
       </c>
       <c r="L31" s="8" t="str">
         <f t="shared" si="8"/>
-        <v>k</v>
+        <v>1.7M</v>
       </c>
       <c r="M31" s="8" t="str">
         <f>TEXT(SUMIFS(raw_output!$L$2:$L$197,raw_output!$M$2:$M$197,'Overall Output. Labeled'!$N31,raw_output!$A$2:$A$197,'Overall Output. Labeled'!$U31,raw_output!$B$2:$B$197,'Overall Output. Labeled'!$S31,raw_output!$C$2:$C$197,'Overall Output. Labeled'!$T31,raw_output!$D$2:$D$197,'Overall Output. Labeled'!$P31,raw_output!$E$2:$E$197,'Overall Output. Labeled'!$Q31,raw_output!$F$2:$F$197,'Overall Output. Labeled'!$R31),"$#.##")</f>
-        <v>$.</v>
+        <v>$425.39</v>
       </c>
       <c r="N31" s="8">
         <v>0.01</v>
@@ -15880,18 +15879,18 @@
         <v>10</v>
       </c>
       <c r="T31" s="8">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="U31" s="8">
         <v>40</v>
       </c>
       <c r="V31" s="8">
         <f>SUMIFS(raw_output!$K$2:$K$197,raw_output!$A$2:$A$197,'Overall Output. Labeled'!$U31,raw_output!$B$2:$B$197,'Overall Output. Labeled'!$S31,raw_output!$C$2:$C$197,'Overall Output. Labeled'!$T31,raw_output!$D$2:$D$197,'Overall Output. Labeled'!$P31,raw_output!$E$2:$E$197,'Overall Output. Labeled'!$Q31,raw_output!$F$2:$F$197,'Overall Output. Labeled'!$R31,raw_output!$M$2:$M$197,'Overall Output. Labeled'!$N31)</f>
-        <v>0</v>
+        <v>408.38261914938897</v>
       </c>
       <c r="W31" s="8">
         <f t="array" ref="W31">SUMIFS(raw_output!$J$2:$J$197,raw_output!$M$2:$M$197,'Overall Output. Labeled'!$N31,raw_output!$A$2:$A$197,'Overall Output. Labeled'!$U31,raw_output!$B$2:$B$197,'Overall Output. Labeled'!$S31,raw_output!$C$2:$C$197,'Overall Output. Labeled'!$T31,raw_output!$D$2:$D$197,'Overall Output. Labeled'!$P31,raw_output!$E$2:$E$197,'Overall Output. Labeled'!$Q31,raw_output!$F$2:$F$197,'Overall Output. Labeled'!$R31)*1000</f>
-        <v>0</v>
+        <v>1723.1994507107499</v>
       </c>
     </row>
     <row r="32" spans="1:23" x14ac:dyDescent="0.2">
@@ -16121,7 +16120,7 @@
     </row>
     <row r="39" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="40" spans="1:23" x14ac:dyDescent="0.2">
@@ -16134,7 +16133,7 @@
     </row>
     <row r="41" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A41" s="24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B41" s="24"/>
       <c r="C41" s="24"/>
@@ -16142,7 +16141,7 @@
     </row>
     <row r="42" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A42" s="29" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B42" s="29"/>
       <c r="C42" s="29"/>
@@ -16150,7 +16149,7 @@
     </row>
     <row r="43" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -16158,12 +16157,12 @@
     </row>
     <row r="45" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C45" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="49" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A49" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B49" s="8"/>
       <c r="C49" s="8" t="s">
@@ -16238,11 +16237,11 @@
     </row>
     <row r="50" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B50" s="8"/>
       <c r="C50" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D50" s="8"/>
       <c r="E50" s="8"/>
@@ -16313,7 +16312,7 @@
     </row>
     <row r="51" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B51" s="8"/>
       <c r="C51" s="8" t="s">
@@ -16388,7 +16387,7 @@
     </row>
     <row r="52" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A52" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B52" s="8"/>
       <c r="C52" s="8" t="s">
@@ -16463,11 +16462,11 @@
     </row>
     <row r="53" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A53" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B53" s="8"/>
       <c r="C53" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D53" s="8"/>
       <c r="E53" s="8"/>
@@ -16538,11 +16537,11 @@
     </row>
     <row r="54" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A54" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B54" s="8"/>
       <c r="C54" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D54" s="8"/>
       <c r="E54" s="8"/>
@@ -16613,11 +16612,11 @@
     </row>
     <row r="55" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A55" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B55" s="8"/>
       <c r="C55" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D55" s="8"/>
       <c r="E55" s="8"/>
@@ -16688,11 +16687,11 @@
     </row>
     <row r="56" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A56" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B56" s="8"/>
       <c r="C56" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D56" s="8"/>
       <c r="E56" s="8"/>
@@ -16763,11 +16762,11 @@
     </row>
     <row r="57" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A57" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B57" s="8"/>
       <c r="C57" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D57" s="8"/>
       <c r="E57" s="8"/>
@@ -16838,11 +16837,11 @@
     </row>
     <row r="58" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A58" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B58" s="8"/>
       <c r="C58" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D58" s="8"/>
       <c r="E58" s="8"/>
@@ -16913,11 +16912,11 @@
     </row>
     <row r="59" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A59" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B59" s="8"/>
       <c r="C59" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D59" s="8"/>
       <c r="E59" s="8"/>
@@ -16988,11 +16987,11 @@
     </row>
     <row r="60" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A60" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B60" s="8"/>
       <c r="C60" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D60" s="8"/>
       <c r="E60" s="8"/>
@@ -17063,11 +17062,11 @@
     </row>
     <row r="61" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A61" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B61" s="8"/>
       <c r="C61" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D61" s="8"/>
       <c r="E61" s="8"/>
@@ -17138,11 +17137,11 @@
     </row>
     <row r="62" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A62" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B62" s="8"/>
       <c r="C62" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D62" s="8"/>
       <c r="E62" s="8"/>
@@ -17213,11 +17212,11 @@
     </row>
     <row r="63" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A63" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B63" s="8"/>
       <c r="C63" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D63" s="8"/>
       <c r="E63" s="8"/>
@@ -17288,11 +17287,11 @@
     </row>
     <row r="64" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A64" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B64" s="8"/>
       <c r="C64" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D64" s="8"/>
       <c r="E64" s="8"/>
@@ -17363,11 +17362,11 @@
     </row>
     <row r="65" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A65" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B65" s="8"/>
       <c r="C65" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D65" s="8"/>
       <c r="E65" s="8"/>
@@ -17436,11 +17435,11 @@
     </row>
     <row r="66" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A66" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B66" s="8"/>
       <c r="C66" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D66" s="8"/>
       <c r="E66" s="8"/>
@@ -17509,11 +17508,11 @@
     </row>
     <row r="67" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A67" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B67" s="8"/>
       <c r="C67" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D67" s="8"/>
       <c r="E67" s="8"/>
@@ -17582,11 +17581,11 @@
     </row>
     <row r="68" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A68" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B68" s="8"/>
       <c r="C68" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D68" s="8"/>
       <c r="E68" s="8"/>
@@ -17695,13 +17694,13 @@
         <v>30</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="F2" s="11" t="s">
         <v>23</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="17" thickTop="1" x14ac:dyDescent="0.2">
@@ -17736,7 +17735,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="51" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B4" s="51"/>
       <c r="C4" s="51"/>
@@ -17795,7 +17794,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -17818,13 +17817,13 @@
         <v>30</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="F2" s="11" t="s">
         <v>23</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="17" thickTop="1" x14ac:dyDescent="0.2">
@@ -17859,7 +17858,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="51" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B4" s="51"/>
       <c r="C4" s="51"/>
@@ -17918,7 +17917,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B1" s="14"/>
       <c r="C1" s="8"/>
@@ -17939,18 +17938,18 @@
         <v>21</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="F2" s="11" t="s">
         <v>23</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="17" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B3" s="43">
         <f>'Overall Output. Labeled'!F6</f>
@@ -17979,7 +17978,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="42" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B4" s="40">
         <f>'Overall Output. Labeled'!F5</f>
@@ -18008,7 +18007,7 @@
     </row>
     <row r="5" spans="1:7" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="52" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B5" s="52"/>
       <c r="C5" s="52"/>
@@ -18055,7 +18054,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2175438C-31AA-F346-960E-642C0B634EAF}">
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.83203125" customWidth="1"/>
@@ -18064,34 +18063,37 @@
     <col min="4" max="4" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
       <c r="D1" s="8"/>
     </row>
-    <row r="2" spans="1:4" ht="65" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="69" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="B2" s="10" t="s">
-        <v>69</v>
-      </c>
       <c r="C2" s="10" t="s">
-        <v>62</v>
+        <v>175</v>
       </c>
       <c r="D2" s="11" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" ht="64" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="E2" s="11" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="64" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A3" s="53" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C3" s="19" t="str">
         <f>'Overall Output. Labeled'!J7</f>
@@ -18101,11 +18103,15 @@
         <f>'Overall Output. Labeled'!K7</f>
         <v>$2.4T</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="64" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E3" s="19" t="str">
+        <f>'Overall Output. Labeled'!L7</f>
+        <v>275k</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="54"/>
       <c r="B4" s="17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C4" s="23" t="str">
         <f>'Overall Output. Labeled'!J8</f>
@@ -18115,61 +18121,68 @@
         <f>'Overall Output. Labeled'!K8</f>
         <v>$4.2T</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E4" s="23" t="str">
+        <f>'Overall Output. Labeled'!L8</f>
+        <v>460k</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B5" s="51"/>
       <c r="C5" s="51"/>
       <c r="D5" s="51"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="52"/>
       <c r="B6" s="52"/>
       <c r="C6" s="52"/>
       <c r="D6" s="52"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="52"/>
       <c r="B7" s="52"/>
       <c r="C7" s="52"/>
       <c r="D7" s="52"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="52"/>
       <c r="B8" s="52"/>
       <c r="C8" s="52"/>
       <c r="D8" s="52"/>
     </row>
-    <row r="11" spans="1:4" ht="21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="21" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
     </row>
-    <row r="12" spans="1:4" ht="69" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" ht="69" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>69</v>
-      </c>
       <c r="C12" s="10" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" ht="120" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="E12" s="11" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="120" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A13" s="22" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C13" s="19" t="str">
         <f>C3</f>
@@ -18179,13 +18192,17 @@
         <f>D3</f>
         <v>$2.4T</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" ht="102" x14ac:dyDescent="0.2">
+      <c r="E13" s="19" t="str">
+        <f>E3</f>
+        <v>275k</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="102" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C14" s="23" t="str">
         <f>'Overall Output. Labeled'!J9</f>
@@ -18195,13 +18212,17 @@
         <f>'Overall Output. Labeled'!K9</f>
         <v>$22.2T</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" ht="17" x14ac:dyDescent="0.2">
+      <c r="E14" s="23" t="str">
+        <f>'Overall Output. Labeled'!L9</f>
+        <v>1.1M</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C15" s="19" t="str">
         <f>'Overall Output. Labeled'!J10</f>
@@ -18211,61 +18232,68 @@
         <f>'Overall Output. Labeled'!K10</f>
         <v>$36.2T</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E15" s="58" t="str">
+        <f>'Overall Output. Labeled'!L10</f>
+        <v>650k</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B16" s="51"/>
       <c r="C16" s="51"/>
       <c r="D16" s="51"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="52"/>
       <c r="B17" s="52"/>
       <c r="C17" s="52"/>
       <c r="D17" s="52"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" s="52"/>
       <c r="B18" s="52"/>
       <c r="C18" s="52"/>
       <c r="D18" s="52"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" s="52"/>
       <c r="B19" s="52"/>
       <c r="C19" s="52"/>
       <c r="D19" s="52"/>
     </row>
-    <row r="22" spans="1:4" ht="21" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" ht="21" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B22" s="8"/>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
     </row>
-    <row r="23" spans="1:4" ht="69" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" ht="69" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="B23" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="B23" s="10" t="s">
-        <v>69</v>
-      </c>
       <c r="C23" s="10" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" ht="91" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="E23" s="11" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="91" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A24" s="17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C24" s="23" t="str">
         <f>C14</f>
@@ -18275,13 +18303,17 @@
         <f>D14</f>
         <v>$22.2T</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" ht="102" x14ac:dyDescent="0.2">
+      <c r="E24" s="23" t="str">
+        <f>E14</f>
+        <v>1.1M</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="102" x14ac:dyDescent="0.2">
       <c r="A25" s="17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C25" s="23" t="str">
         <f>'Overall Output. Labeled'!J11</f>
@@ -18291,13 +18323,17 @@
         <f>'Overall Output. Labeled'!K11</f>
         <v>$23.3T</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E25" s="23" t="str">
+        <f>'Overall Output. Labeled'!L11</f>
+        <v>1.3M</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B26" s="38" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C26" s="39" t="str">
         <f>'Overall Output. Labeled'!J12</f>
@@ -18307,28 +18343,32 @@
         <f>'Overall Output. Labeled'!K12</f>
         <v>$2.0T</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E26" s="59" t="str">
+        <f>'Overall Output. Labeled'!L12</f>
+        <v>221k</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B27" s="51"/>
       <c r="C27" s="51"/>
       <c r="D27" s="51"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="52"/>
       <c r="B28" s="52"/>
       <c r="C28" s="52"/>
       <c r="D28" s="52"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="52"/>
       <c r="B29" s="52"/>
       <c r="C29" s="52"/>
       <c r="D29" s="52"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="52"/>
       <c r="B30" s="52"/>
       <c r="C30" s="52"/>
@@ -18361,7 +18401,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -18384,13 +18424,13 @@
         <v>30</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="F2" s="11" t="s">
         <v>23</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="17" thickTop="1" x14ac:dyDescent="0.2">
@@ -18425,7 +18465,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="51" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B4" s="51"/>
       <c r="C4" s="51"/>
@@ -18463,7 +18503,7 @@
     </row>
     <row r="10" spans="1:7" ht="21" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -18486,13 +18526,13 @@
         <v>30</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="F11" s="11" t="s">
         <v>23</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="17" thickTop="1" x14ac:dyDescent="0.2">
@@ -18617,7 +18657,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="51" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B16" s="51"/>
       <c r="C16" s="51"/>
@@ -18676,7 +18716,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -18684,10 +18724,10 @@
     </row>
     <row r="2" spans="1:4" ht="49" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>95</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>96</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>23</v>
@@ -18698,7 +18738,7 @@
     </row>
     <row r="3" spans="1:4" ht="40" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A3" s="18" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B3" s="25">
         <v>1</v>
@@ -18714,7 +18754,7 @@
     </row>
     <row r="4" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="17" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B4" s="46">
         <v>1</v>
@@ -18730,7 +18770,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="51" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B5" s="51"/>
       <c r="C5" s="51"/>
@@ -18756,7 +18796,7 @@
     </row>
     <row r="11" spans="1:4" ht="21" x14ac:dyDescent="0.25">
       <c r="A11" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -18764,21 +18804,21 @@
     </row>
     <row r="12" spans="1:4" ht="49" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B12" s="10" t="s">
         <v>95</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>96</v>
       </c>
       <c r="C12" s="11" t="s">
         <v>23</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="68" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A13" s="18" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B13" s="25">
         <v>1</v>
@@ -18788,7 +18828,7 @@
         <v>$36.0T</v>
       </c>
       <c r="D13" s="28" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="68" x14ac:dyDescent="0.2">
@@ -18800,15 +18840,15 @@
       </c>
       <c r="C14" s="40" t="str">
         <f>'Overall Output. Labeled'!K20</f>
-        <v>$.0T</v>
+        <v>$38.4T</v>
       </c>
       <c r="D14" s="48" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="51" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B15" s="51"/>
       <c r="C15" s="51"/>
@@ -18872,7 +18912,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B1" s="8"/>
       <c r="C1" s="8"/>
@@ -18880,10 +18920,10 @@
     </row>
     <row r="2" spans="1:4" ht="52" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>62</v>
+        <v>175</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>23</v>
@@ -18894,7 +18934,7 @@
     </row>
     <row r="3" spans="1:4" ht="54" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A3" s="18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B3" s="30" t="str">
         <f>'Overall Output. Labeled'!J21</f>
@@ -18911,10 +18951,10 @@
     </row>
     <row r="4" spans="1:4" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="18" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C4" s="30" t="str">
         <f>'Overall Output. Labeled'!K22</f>
@@ -18927,7 +18967,7 @@
     </row>
     <row r="5" spans="1:4" ht="55" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="18" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B5" s="30" t="str">
         <f>'Overall Output. Labeled'!J23</f>
@@ -18944,7 +18984,7 @@
     </row>
     <row r="6" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="51" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B6" s="51"/>
       <c r="C6" s="51"/>
@@ -18988,7 +19028,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="49" thickBot="1" x14ac:dyDescent="0.25">
@@ -18999,12 +19039,12 @@
         <v>23</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="35" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A17" s="18" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B17" s="30" t="str">
         <f>'Overall Output. Labeled'!K7</f>
@@ -19017,7 +19057,7 @@
     </row>
     <row r="18" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A18" s="18" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B18" s="30" t="str">
         <f>'Overall Output. Labeled'!K3</f>
@@ -19030,7 +19070,7 @@
     </row>
     <row r="19" spans="1:4" ht="34" x14ac:dyDescent="0.2">
       <c r="A19" s="18" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B19" s="30" t="str">
         <f>'Overall Output. Labeled'!K4</f>
@@ -19043,7 +19083,7 @@
     </row>
     <row r="20" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A20" s="18" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B20" s="30" t="str">
         <f>'Overall Output. Labeled'!K5</f>
@@ -19056,7 +19096,7 @@
     </row>
     <row r="21" spans="1:4" ht="51" x14ac:dyDescent="0.2">
       <c r="A21" s="18" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B21" s="30" t="str">
         <f>'Overall Output. Labeled'!K13</f>
@@ -19069,7 +19109,7 @@
     </row>
     <row r="22" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="51" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B22" s="51"/>
       <c r="C22" s="51"/>
